--- a/artfynd/A 15203-2026 artfynd.xlsx
+++ b/artfynd/A 15203-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,7 +1014,7 @@
         <v>132904063</v>
       </c>
       <c r="B5" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>132908714</v>
       </c>
       <c r="B6" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,6 +1335,1190 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132909362</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468421</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6770374</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132910711</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468270</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6770175</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132908892</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468417</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6770492</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132904391</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468259</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6770204</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132909193</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468409</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6770437</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132904273</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>468245</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6770183</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132904531</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>468286</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6770204</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132905740</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>468352</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6770275</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132904538</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>468286</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6770204</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132909261</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>468428</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6770384</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132904778</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>468275</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6770228</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132909129</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79329</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468420</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6770447</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15203-2026 artfynd.xlsx
+++ b/artfynd/A 15203-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132908870</v>
+        <v>132906405</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sästjärnen, Sästjärnen, Dlr</t>
+          <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468401</v>
+        <v>468288</v>
       </c>
       <c r="R2" t="n">
-        <v>6770437</v>
+        <v>6770305</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +747,9 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +764,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132909142</v>
+        <v>132904063</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sästjärnen, Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468424</v>
+        <v>468262</v>
       </c>
       <c r="R3" t="n">
-        <v>6770437</v>
+        <v>6770186</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +844,14 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:55</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sparsamt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132904901</v>
+        <v>132904273</v>
       </c>
       <c r="B4" t="n">
-        <v>8455</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sästjärnen, Sästjärnen, Dlr</t>
+          <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468288</v>
+        <v>468245</v>
       </c>
       <c r="R4" t="n">
-        <v>6770242</v>
+        <v>6770183</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,19 +946,9 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,26 +963,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132904063</v>
+        <v>132904391</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1042,17 +1006,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sästjärnen, Sästjärnen, Dlr</t>
+          <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468262</v>
+        <v>468259</v>
       </c>
       <c r="R5" t="n">
-        <v>6770186</v>
+        <v>6770204</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sparsamt på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,26 +1060,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132908714</v>
+        <v>132904778</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1144,17 +1103,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sästjärnen, Sästjärnen, Dlr</t>
+          <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468401</v>
+        <v>468275</v>
       </c>
       <c r="R6" t="n">
-        <v>6770437</v>
+        <v>6770228</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,24 +1140,9 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sparsamt på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,62 +1157,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132906241</v>
+        <v>132905089</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sästjärnen, Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468339</v>
+        <v>468319</v>
       </c>
       <c r="R7" t="n">
-        <v>6770288</v>
+        <v>6770248</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1300,7 +1239,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1249,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,14 +1281,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132909362</v>
+        <v>132905740</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1372,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468421</v>
+        <v>468352</v>
       </c>
       <c r="R8" t="n">
-        <v>6770374</v>
+        <v>6770275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,53 +1378,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132910711</v>
+        <v>132908714</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sästjärnen, Dlr</t>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468270</v>
+        <v>468401</v>
       </c>
       <c r="R9" t="n">
-        <v>6770175</v>
+        <v>6770437</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,9 +1446,24 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sparsamt på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,62 +1478,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132908892</v>
+        <v>132909129</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468417</v>
+        <v>468420</v>
       </c>
       <c r="R10" t="n">
-        <v>6770492</v>
+        <v>6770447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,14 +1587,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132904391</v>
+        <v>132909193</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1673,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468259</v>
+        <v>468409</v>
       </c>
       <c r="R11" t="n">
-        <v>6770204</v>
+        <v>6770437</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,14 +1684,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132909193</v>
+        <v>132909261</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1770,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468409</v>
+        <v>468428</v>
       </c>
       <c r="R12" t="n">
-        <v>6770437</v>
+        <v>6770384</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,14 +1781,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132904273</v>
+        <v>132909362</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1867,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468245</v>
+        <v>468421</v>
       </c>
       <c r="R13" t="n">
-        <v>6770183</v>
+        <v>6770374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,11 +1881,11 @@
         <v>132904531</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2031,45 +1980,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132905740</v>
+        <v>132906185</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468352</v>
+        <v>468271</v>
       </c>
       <c r="R15" t="n">
-        <v>6770275</v>
+        <v>6770325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2082,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132904538</v>
+        <v>132906301</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,27 +2093,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2168,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468286</v>
+        <v>468288</v>
       </c>
       <c r="R16" t="n">
-        <v>6770204</v>
+        <v>6770305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,45 +2184,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132909261</v>
+        <v>132908892</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468428</v>
+        <v>468417</v>
       </c>
       <c r="R17" t="n">
-        <v>6770384</v>
+        <v>6770492</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,48 +2286,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132904778</v>
+        <v>132909523</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sästjärnen, Dlr</t>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468275</v>
+        <v>468385</v>
       </c>
       <c r="R18" t="n">
-        <v>6770228</v>
+        <v>6770315</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2395,9 +2359,19 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2412,60 +2386,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132909129</v>
+        <v>132910711</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sästjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468420</v>
+        <v>468270</v>
       </c>
       <c r="R19" t="n">
-        <v>6770447</v>
+        <v>6770175</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2518,6 +2497,1566 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132904287</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468232</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6770189</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132904538</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468286</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6770204</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132904901</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>468288</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6770242</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132906189</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>468271</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6770325</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132906241</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>468339</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6770288</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132908870</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>468401</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6770437</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132909142</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>468424</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6770437</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132904441</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>468232</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6770189</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132905381</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>468305</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6770271</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132905673</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>468339</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6770288</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132905698</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>468352</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6770275</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132906471</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>468288</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6770305</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132908432</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>468377</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6770392</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132908528</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>468380</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6770430</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132909134</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sästjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>468420</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6770447</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15203-2026 artfynd.xlsx
+++ b/artfynd/A 15203-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904441</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132906405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904391</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904778</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132905089</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132905740</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908714</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909129</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909193</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909261</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909362</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2186,6 +2261,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904531</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132906185</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2390,6 +2475,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132906301</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908892</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2604,6 +2699,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909523</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132910711</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2808,6 +2913,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904538</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2920,6 +3030,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904901</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3022,6 +3137,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132906189</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,6 +3254,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132906241</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3246,6 +3371,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908870</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3358,6 +3488,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909142</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3455,6 +3590,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132905381</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132905673</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3659,6 +3804,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132905698</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3756,6 +3906,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132906471</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3863,6 +4018,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908432</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3960,6 +4120,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908528</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4057,8 +4222,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>